--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:42:02+08:00</t>
+    <t>2026-07-10T19:56:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T19:56:53+08:00</t>
+    <t>2026-07-10T21:30:50+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T21:30:50+08:00</t>
+    <t>2026-07-23T22:22:27+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:22:27+08:00</t>
+    <t>2026-07-24T13:54:16+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -36,28 +36,31 @@
     <t>Name</t>
   </si>
   <si>
-    <t>sf-BetNutChewAmount-valueset</t>
+    <t>SFBetNutChewAmountValueSet</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>每日嚼檳榔量值集</t>
+    <t>【本地 stub】每日嚼檳榔量值集（非權威定義）</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:45:10+08:00</t>
+    <t>2026-07-29T09:46:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +94,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>權威定義來源為臺灣癌症登記短表 IG（TWCR_SF）。本 IG 僅為建置與驗證所需之局部複本（content = fragment），非權威定義；實作端應以 TWCR_SF 官方定義為準。</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -301,74 +307,78 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>27</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -387,28 +397,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-sf-BetNutChewAmount-valueset.xlsx
+++ b/ValueSet-sf-BetNutChewAmount-valueset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
